--- a/data/derived_data/2_RarefyData/Dataset_2/ps_16S_cl_Dataset_2_tax_table.xlsx
+++ b/data/derived_data/2_RarefyData/Dataset_2/ps_16S_cl_Dataset_2_tax_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="1259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="1260">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -2253,6 +2253,9 @@
   </si>
   <si>
     <t xml:space="preserve">Cluster_337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tatumella</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_338</t>
@@ -10923,7 +10926,7 @@
         <v>45</v>
       </c>
       <c r="G262" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H262" t="s">
         <v>212</v>
@@ -16435,7 +16438,7 @@
         <v>49</v>
       </c>
       <c r="G474" t="s">
-        <v>15</v>
+        <v>747</v>
       </c>
       <c r="H474" t="s">
         <v>15</v>
@@ -16443,7 +16446,7 @@
     </row>
     <row r="475">
       <c r="A475" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B475" t="s">
         <v>9</v>
@@ -16461,15 +16464,15 @@
         <v>399</v>
       </c>
       <c r="G475" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H475" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B476" t="s">
         <v>9</v>
@@ -16487,7 +16490,7 @@
         <v>204</v>
       </c>
       <c r="G476" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H476" t="s">
         <v>15</v>
@@ -16495,7 +16498,7 @@
     </row>
     <row r="477">
       <c r="A477" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B477" t="s">
         <v>9</v>
@@ -16521,7 +16524,7 @@
     </row>
     <row r="478">
       <c r="A478" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B478" t="s">
         <v>9</v>
@@ -16547,7 +16550,7 @@
     </row>
     <row r="479">
       <c r="A479" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B479" t="s">
         <v>9</v>
@@ -16573,7 +16576,7 @@
     </row>
     <row r="480">
       <c r="A480" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B480" t="s">
         <v>9</v>
@@ -16591,7 +16594,7 @@
         <v>165</v>
       </c>
       <c r="G480" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H480" t="s">
         <v>15</v>
@@ -16599,7 +16602,7 @@
     </row>
     <row r="481">
       <c r="A481" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B481" t="s">
         <v>9</v>
@@ -16625,7 +16628,7 @@
     </row>
     <row r="482">
       <c r="A482" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B482" t="s">
         <v>9</v>
@@ -16651,7 +16654,7 @@
     </row>
     <row r="483">
       <c r="A483" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B483" t="s">
         <v>9</v>
@@ -16677,7 +16680,7 @@
     </row>
     <row r="484">
       <c r="A484" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B484" t="s">
         <v>9</v>
@@ -16703,7 +16706,7 @@
     </row>
     <row r="485">
       <c r="A485" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B485" t="s">
         <v>9</v>
@@ -16729,7 +16732,7 @@
     </row>
     <row r="486">
       <c r="A486" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B486" t="s">
         <v>9</v>
@@ -16755,7 +16758,7 @@
     </row>
     <row r="487">
       <c r="A487" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B487" t="s">
         <v>9</v>
@@ -16781,7 +16784,7 @@
     </row>
     <row r="488">
       <c r="A488" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B488" t="s">
         <v>9</v>
@@ -16799,7 +16802,7 @@
         <v>76</v>
       </c>
       <c r="G488" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H488" t="s">
         <v>15</v>
@@ -16807,7 +16810,7 @@
     </row>
     <row r="489">
       <c r="A489" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B489" t="s">
         <v>9</v>
@@ -16833,7 +16836,7 @@
     </row>
     <row r="490">
       <c r="A490" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B490" t="s">
         <v>9</v>
@@ -16859,7 +16862,7 @@
     </row>
     <row r="491">
       <c r="A491" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B491" t="s">
         <v>9</v>
@@ -16885,7 +16888,7 @@
     </row>
     <row r="492">
       <c r="A492" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B492" t="s">
         <v>9</v>
@@ -16911,7 +16914,7 @@
     </row>
     <row r="493">
       <c r="A493" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B493" t="s">
         <v>9</v>
@@ -16937,7 +16940,7 @@
     </row>
     <row r="494">
       <c r="A494" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B494" t="s">
         <v>9</v>
@@ -16963,7 +16966,7 @@
     </row>
     <row r="495">
       <c r="A495" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B495" t="s">
         <v>9</v>
@@ -16989,7 +16992,7 @@
     </row>
     <row r="496">
       <c r="A496" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B496" t="s">
         <v>9</v>
@@ -17015,7 +17018,7 @@
     </row>
     <row r="497">
       <c r="A497" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B497" t="s">
         <v>9</v>
@@ -17041,7 +17044,7 @@
     </row>
     <row r="498">
       <c r="A498" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B498" t="s">
         <v>9</v>
@@ -17067,7 +17070,7 @@
     </row>
     <row r="499">
       <c r="A499" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B499" t="s">
         <v>9</v>
@@ -17093,7 +17096,7 @@
     </row>
     <row r="500">
       <c r="A500" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B500" t="s">
         <v>9</v>
@@ -17119,7 +17122,7 @@
     </row>
     <row r="501">
       <c r="A501" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B501" t="s">
         <v>9</v>
@@ -17145,7 +17148,7 @@
     </row>
     <row r="502">
       <c r="A502" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B502" t="s">
         <v>9</v>
@@ -17171,7 +17174,7 @@
     </row>
     <row r="503">
       <c r="A503" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B503" t="s">
         <v>9</v>
@@ -17197,7 +17200,7 @@
     </row>
     <row r="504">
       <c r="A504" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B504" t="s">
         <v>9</v>
@@ -17223,7 +17226,7 @@
     </row>
     <row r="505">
       <c r="A505" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B505" t="s">
         <v>9</v>
@@ -17249,7 +17252,7 @@
     </row>
     <row r="506">
       <c r="A506" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B506" t="s">
         <v>9</v>
@@ -17275,7 +17278,7 @@
     </row>
     <row r="507">
       <c r="A507" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B507" t="s">
         <v>9</v>
@@ -17301,7 +17304,7 @@
     </row>
     <row r="508">
       <c r="A508" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B508" t="s">
         <v>9</v>
@@ -17327,7 +17330,7 @@
     </row>
     <row r="509">
       <c r="A509" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B509" t="s">
         <v>9</v>
@@ -17353,7 +17356,7 @@
     </row>
     <row r="510">
       <c r="A510" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B510" t="s">
         <v>9</v>
@@ -17371,7 +17374,7 @@
         <v>5</v>
       </c>
       <c r="G510" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H510" t="s">
         <v>15</v>
@@ -17379,7 +17382,7 @@
     </row>
     <row r="511">
       <c r="A511" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B511" t="s">
         <v>9</v>
@@ -17405,7 +17408,7 @@
     </row>
     <row r="512">
       <c r="A512" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B512" t="s">
         <v>9</v>
@@ -17431,7 +17434,7 @@
     </row>
     <row r="513">
       <c r="A513" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B513" t="s">
         <v>9</v>
@@ -17457,7 +17460,7 @@
     </row>
     <row r="514">
       <c r="A514" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B514" t="s">
         <v>9</v>
@@ -17483,7 +17486,7 @@
     </row>
     <row r="515">
       <c r="A515" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B515" t="s">
         <v>9</v>
@@ -17509,7 +17512,7 @@
     </row>
     <row r="516">
       <c r="A516" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B516" t="s">
         <v>9</v>
@@ -17524,7 +17527,7 @@
         <v>312</v>
       </c>
       <c r="F516" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G516" t="s">
         <v>15</v>
@@ -17535,7 +17538,7 @@
     </row>
     <row r="517">
       <c r="A517" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B517" t="s">
         <v>9</v>
@@ -17561,7 +17564,7 @@
     </row>
     <row r="518">
       <c r="A518" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B518" t="s">
         <v>9</v>
@@ -17587,7 +17590,7 @@
     </row>
     <row r="519">
       <c r="A519" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B519" t="s">
         <v>9</v>
@@ -17613,7 +17616,7 @@
     </row>
     <row r="520">
       <c r="A520" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B520" t="s">
         <v>9</v>
@@ -17639,7 +17642,7 @@
     </row>
     <row r="521">
       <c r="A521" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B521" t="s">
         <v>9</v>
@@ -17654,10 +17657,10 @@
         <v>67</v>
       </c>
       <c r="F521" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G521" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H521" t="s">
         <v>15</v>
@@ -17665,7 +17668,7 @@
     </row>
     <row r="522">
       <c r="A522" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B522" t="s">
         <v>9</v>
@@ -17691,7 +17694,7 @@
     </row>
     <row r="523">
       <c r="A523" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B523" t="s">
         <v>9</v>
@@ -17717,7 +17720,7 @@
     </row>
     <row r="524">
       <c r="A524" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B524" t="s">
         <v>9</v>
@@ -17738,12 +17741,12 @@
         <v>162</v>
       </c>
       <c r="H524" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B525" t="s">
         <v>9</v>
@@ -17769,7 +17772,7 @@
     </row>
     <row r="526">
       <c r="A526" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B526" t="s">
         <v>9</v>
@@ -17795,7 +17798,7 @@
     </row>
     <row r="527">
       <c r="A527" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B527" t="s">
         <v>9</v>
@@ -17821,7 +17824,7 @@
     </row>
     <row r="528">
       <c r="A528" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B528" t="s">
         <v>9</v>
@@ -17847,7 +17850,7 @@
     </row>
     <row r="529">
       <c r="A529" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B529" t="s">
         <v>9</v>
@@ -17873,7 +17876,7 @@
     </row>
     <row r="530">
       <c r="A530" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B530" t="s">
         <v>9</v>
@@ -17888,10 +17891,10 @@
         <v>67</v>
       </c>
       <c r="F530" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="G530" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H530" t="s">
         <v>15</v>
@@ -17899,7 +17902,7 @@
     </row>
     <row r="531">
       <c r="A531" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B531" t="s">
         <v>9</v>
@@ -17925,7 +17928,7 @@
     </row>
     <row r="532">
       <c r="A532" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B532" t="s">
         <v>9</v>
@@ -17951,7 +17954,7 @@
     </row>
     <row r="533">
       <c r="A533" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B533" t="s">
         <v>9</v>
@@ -17977,7 +17980,7 @@
     </row>
     <row r="534">
       <c r="A534" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B534" t="s">
         <v>9</v>
@@ -18003,7 +18006,7 @@
     </row>
     <row r="535">
       <c r="A535" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B535" t="s">
         <v>9</v>
@@ -18029,7 +18032,7 @@
     </row>
     <row r="536">
       <c r="A536" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B536" t="s">
         <v>9</v>
@@ -18055,7 +18058,7 @@
     </row>
     <row r="537">
       <c r="A537" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B537" t="s">
         <v>9</v>
@@ -18081,7 +18084,7 @@
     </row>
     <row r="538">
       <c r="A538" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B538" t="s">
         <v>9</v>
@@ -18107,7 +18110,7 @@
     </row>
     <row r="539">
       <c r="A539" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B539" t="s">
         <v>9</v>
@@ -18133,7 +18136,7 @@
     </row>
     <row r="540">
       <c r="A540" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B540" t="s">
         <v>9</v>
@@ -18159,7 +18162,7 @@
     </row>
     <row r="541">
       <c r="A541" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B541" t="s">
         <v>9</v>
@@ -18185,7 +18188,7 @@
     </row>
     <row r="542">
       <c r="A542" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B542" t="s">
         <v>9</v>
@@ -18211,7 +18214,7 @@
     </row>
     <row r="543">
       <c r="A543" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B543" t="s">
         <v>9</v>
@@ -18237,7 +18240,7 @@
     </row>
     <row r="544">
       <c r="A544" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B544" t="s">
         <v>9</v>
@@ -18263,7 +18266,7 @@
     </row>
     <row r="545">
       <c r="A545" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B545" t="s">
         <v>9</v>
@@ -18289,7 +18292,7 @@
     </row>
     <row r="546">
       <c r="A546" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B546" t="s">
         <v>9</v>
@@ -18307,7 +18310,7 @@
         <v>120</v>
       </c>
       <c r="G546" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H546" t="s">
         <v>15</v>
@@ -18315,7 +18318,7 @@
     </row>
     <row r="547">
       <c r="A547" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B547" t="s">
         <v>9</v>
@@ -18341,7 +18344,7 @@
     </row>
     <row r="548">
       <c r="A548" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B548" t="s">
         <v>9</v>
@@ -18367,7 +18370,7 @@
     </row>
     <row r="549">
       <c r="A549" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B549" t="s">
         <v>9</v>
@@ -18393,7 +18396,7 @@
     </row>
     <row r="550">
       <c r="A550" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B550" t="s">
         <v>9</v>
@@ -18419,7 +18422,7 @@
     </row>
     <row r="551">
       <c r="A551" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B551" t="s">
         <v>9</v>
@@ -18445,7 +18448,7 @@
     </row>
     <row r="552">
       <c r="A552" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B552" t="s">
         <v>9</v>
@@ -18466,30 +18469,30 @@
         <v>15</v>
       </c>
       <c r="H552" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B553" t="s">
         <v>9</v>
       </c>
       <c r="C553" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D553" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E553" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="F553" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G553" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H553" t="s">
         <v>15</v>
@@ -18497,7 +18500,7 @@
     </row>
     <row r="554">
       <c r="A554" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B554" t="s">
         <v>9</v>
@@ -18523,7 +18526,7 @@
     </row>
     <row r="555">
       <c r="A555" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B555" t="s">
         <v>9</v>
@@ -18549,7 +18552,7 @@
     </row>
     <row r="556">
       <c r="A556" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B556" t="s">
         <v>9</v>
@@ -18575,7 +18578,7 @@
     </row>
     <row r="557">
       <c r="A557" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B557" t="s">
         <v>9</v>
@@ -18601,7 +18604,7 @@
     </row>
     <row r="558">
       <c r="A558" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B558" t="s">
         <v>9</v>
@@ -18627,7 +18630,7 @@
     </row>
     <row r="559">
       <c r="A559" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B559" t="s">
         <v>9</v>
@@ -18653,7 +18656,7 @@
     </row>
     <row r="560">
       <c r="A560" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B560" t="s">
         <v>9</v>
@@ -18674,12 +18677,12 @@
         <v>162</v>
       </c>
       <c r="H560" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B561" t="s">
         <v>9</v>
@@ -18705,7 +18708,7 @@
     </row>
     <row r="562">
       <c r="A562" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B562" t="s">
         <v>9</v>
@@ -18731,7 +18734,7 @@
     </row>
     <row r="563">
       <c r="A563" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B563" t="s">
         <v>9</v>
@@ -18757,7 +18760,7 @@
     </row>
     <row r="564">
       <c r="A564" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B564" t="s">
         <v>9</v>
@@ -18783,7 +18786,7 @@
     </row>
     <row r="565">
       <c r="A565" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B565" t="s">
         <v>9</v>
@@ -18795,13 +18798,13 @@
         <v>222</v>
       </c>
       <c r="E565" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F565" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G565" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H565" t="s">
         <v>15</v>
@@ -18809,7 +18812,7 @@
     </row>
     <row r="566">
       <c r="A566" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B566" t="s">
         <v>9</v>
@@ -18835,7 +18838,7 @@
     </row>
     <row r="567">
       <c r="A567" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B567" t="s">
         <v>9</v>
@@ -18861,7 +18864,7 @@
     </row>
     <row r="568">
       <c r="A568" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B568" t="s">
         <v>9</v>
@@ -18887,7 +18890,7 @@
     </row>
     <row r="569">
       <c r="A569" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B569" t="s">
         <v>9</v>
@@ -18913,7 +18916,7 @@
     </row>
     <row r="570">
       <c r="A570" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B570" t="s">
         <v>9</v>
@@ -18939,7 +18942,7 @@
     </row>
     <row r="571">
       <c r="A571" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B571" t="s">
         <v>9</v>
@@ -18965,7 +18968,7 @@
     </row>
     <row r="572">
       <c r="A572" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B572" t="s">
         <v>9</v>
@@ -18991,7 +18994,7 @@
     </row>
     <row r="573">
       <c r="A573" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B573" t="s">
         <v>9</v>
@@ -19017,7 +19020,7 @@
     </row>
     <row r="574">
       <c r="A574" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B574" t="s">
         <v>9</v>
@@ -19043,7 +19046,7 @@
     </row>
     <row r="575">
       <c r="A575" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B575" t="s">
         <v>9</v>
@@ -19069,7 +19072,7 @@
     </row>
     <row r="576">
       <c r="A576" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B576" t="s">
         <v>9</v>
@@ -19095,7 +19098,7 @@
     </row>
     <row r="577">
       <c r="A577" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B577" t="s">
         <v>9</v>
@@ -19121,7 +19124,7 @@
     </row>
     <row r="578">
       <c r="A578" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B578" t="s">
         <v>9</v>
@@ -19147,7 +19150,7 @@
     </row>
     <row r="579">
       <c r="A579" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B579" t="s">
         <v>9</v>
@@ -19162,10 +19165,10 @@
         <v>12</v>
       </c>
       <c r="F579" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G579" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H579" t="s">
         <v>15</v>
@@ -19173,7 +19176,7 @@
     </row>
     <row r="580">
       <c r="A580" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B580" t="s">
         <v>9</v>
@@ -19199,7 +19202,7 @@
     </row>
     <row r="581">
       <c r="A581" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B581" t="s">
         <v>9</v>
@@ -19225,7 +19228,7 @@
     </row>
     <row r="582">
       <c r="A582" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B582" t="s">
         <v>9</v>
@@ -19251,7 +19254,7 @@
     </row>
     <row r="583">
       <c r="A583" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B583" t="s">
         <v>9</v>
@@ -19266,10 +19269,10 @@
         <v>12</v>
       </c>
       <c r="F583" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G583" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H583" t="s">
         <v>15</v>
@@ -19277,7 +19280,7 @@
     </row>
     <row r="584">
       <c r="A584" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B584" t="s">
         <v>9</v>
@@ -19295,7 +19298,7 @@
         <v>5</v>
       </c>
       <c r="G584" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H584" t="s">
         <v>15</v>
@@ -19303,7 +19306,7 @@
     </row>
     <row r="585">
       <c r="A585" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B585" t="s">
         <v>9</v>
@@ -19329,7 +19332,7 @@
     </row>
     <row r="586">
       <c r="A586" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B586" t="s">
         <v>9</v>
@@ -19355,7 +19358,7 @@
     </row>
     <row r="587">
       <c r="A587" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B587" t="s">
         <v>9</v>
@@ -19381,7 +19384,7 @@
     </row>
     <row r="588">
       <c r="A588" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B588" t="s">
         <v>9</v>
@@ -19407,7 +19410,7 @@
     </row>
     <row r="589">
       <c r="A589" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B589" t="s">
         <v>9</v>
@@ -19433,7 +19436,7 @@
     </row>
     <row r="590">
       <c r="A590" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B590" t="s">
         <v>9</v>
@@ -19448,18 +19451,18 @@
         <v>67</v>
       </c>
       <c r="F590" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G590" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H590" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B591" t="s">
         <v>9</v>
@@ -19485,7 +19488,7 @@
     </row>
     <row r="592">
       <c r="A592" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B592" t="s">
         <v>9</v>
@@ -19503,15 +19506,15 @@
         <v>306</v>
       </c>
       <c r="G592" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H592" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B593" t="s">
         <v>9</v>
@@ -19537,7 +19540,7 @@
     </row>
     <row r="594">
       <c r="A594" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B594" t="s">
         <v>9</v>
@@ -19558,12 +19561,12 @@
         <v>15</v>
       </c>
       <c r="H594" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B595" t="s">
         <v>9</v>
@@ -19589,7 +19592,7 @@
     </row>
     <row r="596">
       <c r="A596" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B596" t="s">
         <v>9</v>
@@ -19615,7 +19618,7 @@
     </row>
     <row r="597">
       <c r="A597" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B597" t="s">
         <v>9</v>
@@ -19641,7 +19644,7 @@
     </row>
     <row r="598">
       <c r="A598" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B598" t="s">
         <v>9</v>
@@ -19667,7 +19670,7 @@
     </row>
     <row r="599">
       <c r="A599" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B599" t="s">
         <v>9</v>
@@ -19685,15 +19688,15 @@
         <v>306</v>
       </c>
       <c r="G599" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H599" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B600" t="s">
         <v>9</v>
@@ -19719,7 +19722,7 @@
     </row>
     <row r="601">
       <c r="A601" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B601" t="s">
         <v>9</v>
@@ -19745,7 +19748,7 @@
     </row>
     <row r="602">
       <c r="A602" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B602" t="s">
         <v>9</v>
@@ -19766,12 +19769,12 @@
         <v>15</v>
       </c>
       <c r="H602" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B603" t="s">
         <v>9</v>
@@ -19797,7 +19800,7 @@
     </row>
     <row r="604">
       <c r="A604" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B604" t="s">
         <v>9</v>
@@ -19823,7 +19826,7 @@
     </row>
     <row r="605">
       <c r="A605" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B605" t="s">
         <v>9</v>
@@ -19849,7 +19852,7 @@
     </row>
     <row r="606">
       <c r="A606" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B606" t="s">
         <v>9</v>
@@ -19875,7 +19878,7 @@
     </row>
     <row r="607">
       <c r="A607" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B607" t="s">
         <v>9</v>
@@ -19901,7 +19904,7 @@
     </row>
     <row r="608">
       <c r="A608" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B608" t="s">
         <v>9</v>
@@ -19927,7 +19930,7 @@
     </row>
     <row r="609">
       <c r="A609" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B609" t="s">
         <v>9</v>
@@ -19953,7 +19956,7 @@
     </row>
     <row r="610">
       <c r="A610" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B610" t="s">
         <v>9</v>
@@ -19979,7 +19982,7 @@
     </row>
     <row r="611">
       <c r="A611" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B611" t="s">
         <v>9</v>
@@ -20005,7 +20008,7 @@
     </row>
     <row r="612">
       <c r="A612" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B612" t="s">
         <v>9</v>
@@ -20031,7 +20034,7 @@
     </row>
     <row r="613">
       <c r="A613" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B613" t="s">
         <v>9</v>
@@ -20057,7 +20060,7 @@
     </row>
     <row r="614">
       <c r="A614" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B614" t="s">
         <v>9</v>
@@ -20083,7 +20086,7 @@
     </row>
     <row r="615">
       <c r="A615" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B615" t="s">
         <v>9</v>
@@ -20109,7 +20112,7 @@
     </row>
     <row r="616">
       <c r="A616" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B616" t="s">
         <v>9</v>
@@ -20127,7 +20130,7 @@
         <v>483</v>
       </c>
       <c r="G616" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H616" t="s">
         <v>15</v>
@@ -20135,7 +20138,7 @@
     </row>
     <row r="617">
       <c r="A617" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B617" t="s">
         <v>9</v>
@@ -20161,7 +20164,7 @@
     </row>
     <row r="618">
       <c r="A618" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B618" t="s">
         <v>9</v>
@@ -20187,7 +20190,7 @@
     </row>
     <row r="619">
       <c r="A619" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B619" t="s">
         <v>9</v>
@@ -20213,7 +20216,7 @@
     </row>
     <row r="620">
       <c r="A620" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B620" t="s">
         <v>9</v>
@@ -20239,7 +20242,7 @@
     </row>
     <row r="621">
       <c r="A621" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B621" t="s">
         <v>9</v>
@@ -20265,7 +20268,7 @@
     </row>
     <row r="622">
       <c r="A622" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B622" t="s">
         <v>9</v>
@@ -20291,7 +20294,7 @@
     </row>
     <row r="623">
       <c r="A623" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B623" t="s">
         <v>9</v>
@@ -20317,7 +20320,7 @@
     </row>
     <row r="624">
       <c r="A624" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B624" t="s">
         <v>9</v>
@@ -20343,7 +20346,7 @@
     </row>
     <row r="625">
       <c r="A625" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B625" t="s">
         <v>9</v>
@@ -20369,7 +20372,7 @@
     </row>
     <row r="626">
       <c r="A626" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B626" t="s">
         <v>9</v>
@@ -20395,7 +20398,7 @@
     </row>
     <row r="627">
       <c r="A627" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B627" t="s">
         <v>9</v>
@@ -20421,7 +20424,7 @@
     </row>
     <row r="628">
       <c r="A628" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B628" t="s">
         <v>9</v>
@@ -20439,7 +20442,7 @@
         <v>83</v>
       </c>
       <c r="G628" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H628" t="s">
         <v>15</v>
@@ -20447,7 +20450,7 @@
     </row>
     <row r="629">
       <c r="A629" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B629" t="s">
         <v>9</v>
@@ -20473,7 +20476,7 @@
     </row>
     <row r="630">
       <c r="A630" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B630" t="s">
         <v>9</v>
@@ -20499,7 +20502,7 @@
     </row>
     <row r="631">
       <c r="A631" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B631" t="s">
         <v>9</v>
@@ -20525,7 +20528,7 @@
     </row>
     <row r="632">
       <c r="A632" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B632" t="s">
         <v>9</v>
@@ -20551,7 +20554,7 @@
     </row>
     <row r="633">
       <c r="A633" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B633" t="s">
         <v>9</v>
@@ -20577,7 +20580,7 @@
     </row>
     <row r="634">
       <c r="A634" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B634" t="s">
         <v>9</v>
@@ -20603,7 +20606,7 @@
     </row>
     <row r="635">
       <c r="A635" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B635" t="s">
         <v>9</v>
@@ -20629,7 +20632,7 @@
     </row>
     <row r="636">
       <c r="A636" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B636" t="s">
         <v>9</v>
@@ -20641,10 +20644,10 @@
         <v>39</v>
       </c>
       <c r="E636" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F636" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="G636" t="s">
         <v>15</v>
@@ -20655,7 +20658,7 @@
     </row>
     <row r="637">
       <c r="A637" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B637" t="s">
         <v>9</v>
@@ -20681,7 +20684,7 @@
     </row>
     <row r="638">
       <c r="A638" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B638" t="s">
         <v>9</v>
@@ -20707,7 +20710,7 @@
     </row>
     <row r="639">
       <c r="A639" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B639" t="s">
         <v>9</v>
@@ -20733,7 +20736,7 @@
     </row>
     <row r="640">
       <c r="A640" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B640" t="s">
         <v>9</v>
@@ -20759,7 +20762,7 @@
     </row>
     <row r="641">
       <c r="A641" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B641" t="s">
         <v>9</v>
@@ -20785,7 +20788,7 @@
     </row>
     <row r="642">
       <c r="A642" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B642" t="s">
         <v>9</v>
@@ -20811,7 +20814,7 @@
     </row>
     <row r="643">
       <c r="A643" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B643" t="s">
         <v>9</v>
@@ -20837,7 +20840,7 @@
     </row>
     <row r="644">
       <c r="A644" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B644" t="s">
         <v>9</v>
@@ -20863,7 +20866,7 @@
     </row>
     <row r="645">
       <c r="A645" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B645" t="s">
         <v>9</v>
@@ -20889,7 +20892,7 @@
     </row>
     <row r="646">
       <c r="A646" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B646" t="s">
         <v>9</v>
@@ -20901,10 +20904,10 @@
         <v>39</v>
       </c>
       <c r="E646" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F646" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="G646" t="s">
         <v>15</v>
@@ -20915,7 +20918,7 @@
     </row>
     <row r="647">
       <c r="A647" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B647" t="s">
         <v>9</v>
@@ -20941,7 +20944,7 @@
     </row>
     <row r="648">
       <c r="A648" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B648" t="s">
         <v>9</v>
@@ -20967,7 +20970,7 @@
     </row>
     <row r="649">
       <c r="A649" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B649" t="s">
         <v>9</v>
@@ -20993,7 +20996,7 @@
     </row>
     <row r="650">
       <c r="A650" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B650" t="s">
         <v>9</v>
@@ -21019,7 +21022,7 @@
     </row>
     <row r="651">
       <c r="A651" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B651" t="s">
         <v>9</v>
@@ -21045,7 +21048,7 @@
     </row>
     <row r="652">
       <c r="A652" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B652" t="s">
         <v>9</v>
@@ -21060,18 +21063,18 @@
         <v>12</v>
       </c>
       <c r="F652" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G652" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H652" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B653" t="s">
         <v>9</v>
@@ -21089,7 +21092,7 @@
         <v>13</v>
       </c>
       <c r="G653" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H653" t="s">
         <v>15</v>
@@ -21097,7 +21100,7 @@
     </row>
     <row r="654">
       <c r="A654" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B654" t="s">
         <v>9</v>
@@ -21115,7 +21118,7 @@
         <v>700</v>
       </c>
       <c r="G654" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H654" t="s">
         <v>15</v>
@@ -21123,7 +21126,7 @@
     </row>
     <row r="655">
       <c r="A655" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B655" t="s">
         <v>9</v>
@@ -21149,7 +21152,7 @@
     </row>
     <row r="656">
       <c r="A656" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B656" t="s">
         <v>9</v>
@@ -21175,7 +21178,7 @@
     </row>
     <row r="657">
       <c r="A657" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B657" t="s">
         <v>9</v>
@@ -21201,7 +21204,7 @@
     </row>
     <row r="658">
       <c r="A658" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B658" t="s">
         <v>9</v>
@@ -21227,7 +21230,7 @@
     </row>
     <row r="659">
       <c r="A659" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B659" t="s">
         <v>9</v>
@@ -21245,7 +21248,7 @@
         <v>49</v>
       </c>
       <c r="G659" t="s">
-        <v>15</v>
+        <v>747</v>
       </c>
       <c r="H659" t="s">
         <v>15</v>
@@ -21253,7 +21256,7 @@
     </row>
     <row r="660">
       <c r="A660" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B660" t="s">
         <v>9</v>
@@ -21274,12 +21277,12 @@
         <v>46</v>
       </c>
       <c r="H660" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B661" t="s">
         <v>9</v>
@@ -21305,7 +21308,7 @@
     </row>
     <row r="662">
       <c r="A662" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B662" t="s">
         <v>9</v>
@@ -21331,7 +21334,7 @@
     </row>
     <row r="663">
       <c r="A663" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B663" t="s">
         <v>9</v>
@@ -21357,7 +21360,7 @@
     </row>
     <row r="664">
       <c r="A664" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B664" t="s">
         <v>9</v>
@@ -21383,7 +21386,7 @@
     </row>
     <row r="665">
       <c r="A665" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B665" t="s">
         <v>9</v>
@@ -21409,7 +21412,7 @@
     </row>
     <row r="666">
       <c r="A666" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B666" t="s">
         <v>9</v>
@@ -21435,7 +21438,7 @@
     </row>
     <row r="667">
       <c r="A667" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B667" t="s">
         <v>9</v>
@@ -21456,12 +21459,12 @@
         <v>46</v>
       </c>
       <c r="H667" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B668" t="s">
         <v>9</v>
@@ -21487,7 +21490,7 @@
     </row>
     <row r="669">
       <c r="A669" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B669" t="s">
         <v>9</v>
@@ -21513,7 +21516,7 @@
     </row>
     <row r="670">
       <c r="A670" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B670" t="s">
         <v>9</v>
@@ -21539,7 +21542,7 @@
     </row>
     <row r="671">
       <c r="A671" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B671" t="s">
         <v>9</v>
@@ -21565,7 +21568,7 @@
     </row>
     <row r="672">
       <c r="A672" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B672" t="s">
         <v>9</v>
@@ -21591,7 +21594,7 @@
     </row>
     <row r="673">
       <c r="A673" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B673" t="s">
         <v>9</v>
@@ -21617,7 +21620,7 @@
     </row>
     <row r="674">
       <c r="A674" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B674" t="s">
         <v>9</v>
@@ -21632,10 +21635,10 @@
         <v>482</v>
       </c>
       <c r="F674" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="G674" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H674" t="s">
         <v>15</v>
@@ -21643,7 +21646,7 @@
     </row>
     <row r="675">
       <c r="A675" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B675" t="s">
         <v>9</v>
@@ -21669,7 +21672,7 @@
     </row>
     <row r="676">
       <c r="A676" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B676" t="s">
         <v>9</v>
@@ -21695,7 +21698,7 @@
     </row>
     <row r="677">
       <c r="A677" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B677" t="s">
         <v>9</v>
@@ -21721,7 +21724,7 @@
     </row>
     <row r="678">
       <c r="A678" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B678" t="s">
         <v>9</v>
@@ -21747,7 +21750,7 @@
     </row>
     <row r="679">
       <c r="A679" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B679" t="s">
         <v>9</v>
@@ -21773,7 +21776,7 @@
     </row>
     <row r="680">
       <c r="A680" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B680" t="s">
         <v>9</v>
@@ -21791,7 +21794,7 @@
         <v>183</v>
       </c>
       <c r="G680" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H680" t="s">
         <v>15</v>
@@ -21799,7 +21802,7 @@
     </row>
     <row r="681">
       <c r="A681" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B681" t="s">
         <v>9</v>
@@ -21825,7 +21828,7 @@
     </row>
     <row r="682">
       <c r="A682" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B682" t="s">
         <v>9</v>
@@ -21851,7 +21854,7 @@
     </row>
     <row r="683">
       <c r="A683" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B683" t="s">
         <v>9</v>
@@ -21869,7 +21872,7 @@
         <v>120</v>
       </c>
       <c r="G683" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H683" t="s">
         <v>15</v>
@@ -21877,7 +21880,7 @@
     </row>
     <row r="684">
       <c r="A684" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B684" t="s">
         <v>9</v>
@@ -21903,7 +21906,7 @@
     </row>
     <row r="685">
       <c r="A685" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B685" t="s">
         <v>9</v>
@@ -21929,7 +21932,7 @@
     </row>
     <row r="686">
       <c r="A686" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B686" t="s">
         <v>9</v>
@@ -21955,7 +21958,7 @@
     </row>
     <row r="687">
       <c r="A687" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B687" t="s">
         <v>9</v>
@@ -21976,12 +21979,12 @@
         <v>15</v>
       </c>
       <c r="H687" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B688" t="s">
         <v>9</v>
@@ -22007,7 +22010,7 @@
     </row>
     <row r="689">
       <c r="A689" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B689" t="s">
         <v>9</v>
@@ -22033,7 +22036,7 @@
     </row>
     <row r="690">
       <c r="A690" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B690" t="s">
         <v>9</v>
@@ -22059,7 +22062,7 @@
     </row>
     <row r="691">
       <c r="A691" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B691" t="s">
         <v>9</v>
@@ -22085,7 +22088,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B692" t="s">
         <v>9</v>
@@ -22111,7 +22114,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B693" t="s">
         <v>9</v>
@@ -22137,7 +22140,7 @@
     </row>
     <row r="694">
       <c r="A694" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B694" t="s">
         <v>9</v>
@@ -22155,7 +22158,7 @@
         <v>57</v>
       </c>
       <c r="G694" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H694" t="s">
         <v>15</v>
@@ -22163,7 +22166,7 @@
     </row>
     <row r="695">
       <c r="A695" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B695" t="s">
         <v>9</v>
@@ -22189,7 +22192,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B696" t="s">
         <v>9</v>
@@ -22210,12 +22213,12 @@
         <v>15</v>
       </c>
       <c r="H696" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B697" t="s">
         <v>9</v>
@@ -22241,7 +22244,7 @@
     </row>
     <row r="698">
       <c r="A698" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B698" t="s">
         <v>9</v>
@@ -22267,7 +22270,7 @@
     </row>
     <row r="699">
       <c r="A699" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B699" t="s">
         <v>9</v>
@@ -22293,7 +22296,7 @@
     </row>
     <row r="700">
       <c r="A700" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B700" t="s">
         <v>9</v>
@@ -22319,7 +22322,7 @@
     </row>
     <row r="701">
       <c r="A701" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B701" t="s">
         <v>9</v>
@@ -22345,7 +22348,7 @@
     </row>
     <row r="702">
       <c r="A702" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B702" t="s">
         <v>9</v>
@@ -22371,7 +22374,7 @@
     </row>
     <row r="703">
       <c r="A703" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B703" t="s">
         <v>9</v>
@@ -22397,7 +22400,7 @@
     </row>
     <row r="704">
       <c r="A704" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B704" t="s">
         <v>9</v>
@@ -22423,7 +22426,7 @@
     </row>
     <row r="705">
       <c r="A705" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B705" t="s">
         <v>9</v>
@@ -22449,7 +22452,7 @@
     </row>
     <row r="706">
       <c r="A706" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B706" t="s">
         <v>9</v>
@@ -22475,7 +22478,7 @@
     </row>
     <row r="707">
       <c r="A707" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B707" t="s">
         <v>9</v>
@@ -22501,7 +22504,7 @@
     </row>
     <row r="708">
       <c r="A708" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B708" t="s">
         <v>9</v>
@@ -22527,7 +22530,7 @@
     </row>
     <row r="709">
       <c r="A709" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B709" t="s">
         <v>9</v>
@@ -22553,7 +22556,7 @@
     </row>
     <row r="710">
       <c r="A710" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B710" t="s">
         <v>9</v>
@@ -22579,7 +22582,7 @@
     </row>
     <row r="711">
       <c r="A711" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B711" t="s">
         <v>9</v>
@@ -22605,22 +22608,22 @@
     </row>
     <row r="712">
       <c r="A712" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B712" t="s">
         <v>9</v>
       </c>
       <c r="C712" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D712" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E712" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F712" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="G712" t="s">
         <v>15</v>
@@ -22631,7 +22634,7 @@
     </row>
     <row r="713">
       <c r="A713" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B713" t="s">
         <v>9</v>
@@ -22657,7 +22660,7 @@
     </row>
     <row r="714">
       <c r="A714" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B714" t="s">
         <v>9</v>
@@ -22683,7 +22686,7 @@
     </row>
     <row r="715">
       <c r="A715" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B715" t="s">
         <v>9</v>
@@ -22709,7 +22712,7 @@
     </row>
     <row r="716">
       <c r="A716" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B716" t="s">
         <v>9</v>
@@ -22735,7 +22738,7 @@
     </row>
     <row r="717">
       <c r="A717" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B717" t="s">
         <v>15</v>
@@ -22761,7 +22764,7 @@
     </row>
     <row r="718">
       <c r="A718" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B718" t="s">
         <v>9</v>
@@ -22787,7 +22790,7 @@
     </row>
     <row r="719">
       <c r="A719" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B719" t="s">
         <v>9</v>
@@ -22813,7 +22816,7 @@
     </row>
     <row r="720">
       <c r="A720" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B720" t="s">
         <v>9</v>
@@ -22839,7 +22842,7 @@
     </row>
     <row r="721">
       <c r="A721" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B721" t="s">
         <v>9</v>
@@ -22857,7 +22860,7 @@
         <v>90</v>
       </c>
       <c r="G721" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H721" t="s">
         <v>15</v>
@@ -22865,7 +22868,7 @@
     </row>
     <row r="722">
       <c r="A722" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B722" t="s">
         <v>9</v>
@@ -22891,7 +22894,7 @@
     </row>
     <row r="723">
       <c r="A723" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B723" t="s">
         <v>9</v>
@@ -22917,7 +22920,7 @@
     </row>
     <row r="724">
       <c r="A724" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B724" t="s">
         <v>9</v>
@@ -22943,7 +22946,7 @@
     </row>
     <row r="725">
       <c r="A725" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B725" t="s">
         <v>9</v>
@@ -22969,7 +22972,7 @@
     </row>
     <row r="726">
       <c r="A726" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B726" t="s">
         <v>9</v>
@@ -22995,7 +22998,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B727" t="s">
         <v>9</v>
@@ -23021,7 +23024,7 @@
     </row>
     <row r="728">
       <c r="A728" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B728" t="s">
         <v>9</v>
@@ -23047,7 +23050,7 @@
     </row>
     <row r="729">
       <c r="A729" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B729" t="s">
         <v>9</v>
@@ -23073,7 +23076,7 @@
     </row>
     <row r="730">
       <c r="A730" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B730" t="s">
         <v>9</v>
@@ -23099,7 +23102,7 @@
     </row>
     <row r="731">
       <c r="A731" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B731" t="s">
         <v>9</v>
@@ -23125,7 +23128,7 @@
     </row>
     <row r="732">
       <c r="A732" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B732" t="s">
         <v>9</v>
@@ -23151,7 +23154,7 @@
     </row>
     <row r="733">
       <c r="A733" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B733" t="s">
         <v>9</v>
@@ -23177,7 +23180,7 @@
     </row>
     <row r="734">
       <c r="A734" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B734" t="s">
         <v>9</v>
@@ -23203,7 +23206,7 @@
     </row>
     <row r="735">
       <c r="A735" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B735" t="s">
         <v>9</v>
@@ -23229,7 +23232,7 @@
     </row>
     <row r="736">
       <c r="A736" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B736" t="s">
         <v>9</v>
@@ -23247,7 +23250,7 @@
         <v>13</v>
       </c>
       <c r="G736" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H736" t="s">
         <v>15</v>
@@ -23255,7 +23258,7 @@
     </row>
     <row r="737">
       <c r="A737" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B737" t="s">
         <v>9</v>
@@ -23273,7 +23276,7 @@
         <v>183</v>
       </c>
       <c r="G737" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H737" t="s">
         <v>15</v>
@@ -23281,7 +23284,7 @@
     </row>
     <row r="738">
       <c r="A738" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B738" t="s">
         <v>9</v>
@@ -23307,7 +23310,7 @@
     </row>
     <row r="739">
       <c r="A739" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B739" t="s">
         <v>9</v>
@@ -23316,16 +23319,16 @@
         <v>65</v>
       </c>
       <c r="D739" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="E739" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F739" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="G739" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H739" t="s">
         <v>15</v>
@@ -23333,7 +23336,7 @@
     </row>
     <row r="740">
       <c r="A740" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B740" t="s">
         <v>9</v>
@@ -23351,7 +23354,7 @@
         <v>231</v>
       </c>
       <c r="G740" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H740" t="s">
         <v>15</v>
@@ -23359,7 +23362,7 @@
     </row>
     <row r="741">
       <c r="A741" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B741" t="s">
         <v>9</v>
@@ -23385,7 +23388,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B742" t="s">
         <v>9</v>
@@ -23411,7 +23414,7 @@
     </row>
     <row r="743">
       <c r="A743" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B743" t="s">
         <v>9</v>
@@ -23426,10 +23429,10 @@
         <v>12</v>
       </c>
       <c r="F743" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G743" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H743" t="s">
         <v>15</v>
@@ -23437,7 +23440,7 @@
     </row>
     <row r="744">
       <c r="A744" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B744" t="s">
         <v>9</v>
@@ -23463,7 +23466,7 @@
     </row>
     <row r="745">
       <c r="A745" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B745" t="s">
         <v>9</v>
@@ -23489,7 +23492,7 @@
     </row>
     <row r="746">
       <c r="A746" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B746" t="s">
         <v>9</v>
@@ -23507,7 +23510,7 @@
         <v>76</v>
       </c>
       <c r="G746" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H746" t="s">
         <v>15</v>
@@ -23515,7 +23518,7 @@
     </row>
     <row r="747">
       <c r="A747" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B747" t="s">
         <v>9</v>
@@ -23541,7 +23544,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B748" t="s">
         <v>9</v>
@@ -23559,7 +23562,7 @@
         <v>68</v>
       </c>
       <c r="G748" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H748" t="s">
         <v>15</v>
@@ -23567,7 +23570,7 @@
     </row>
     <row r="749">
       <c r="A749" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B749" t="s">
         <v>9</v>
@@ -23593,7 +23596,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B750" t="s">
         <v>9</v>
@@ -23619,7 +23622,7 @@
     </row>
     <row r="751">
       <c r="A751" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B751" t="s">
         <v>9</v>
@@ -23645,7 +23648,7 @@
     </row>
     <row r="752">
       <c r="A752" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B752" t="s">
         <v>9</v>
@@ -23671,7 +23674,7 @@
     </row>
     <row r="753">
       <c r="A753" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B753" t="s">
         <v>9</v>
@@ -23697,7 +23700,7 @@
     </row>
     <row r="754">
       <c r="A754" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B754" t="s">
         <v>9</v>
@@ -23723,7 +23726,7 @@
     </row>
     <row r="755">
       <c r="A755" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B755" t="s">
         <v>9</v>
@@ -23749,7 +23752,7 @@
     </row>
     <row r="756">
       <c r="A756" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B756" t="s">
         <v>9</v>
@@ -23775,7 +23778,7 @@
     </row>
     <row r="757">
       <c r="A757" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B757" t="s">
         <v>9</v>
@@ -23801,7 +23804,7 @@
     </row>
     <row r="758">
       <c r="A758" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B758" t="s">
         <v>9</v>
@@ -23819,7 +23822,7 @@
         <v>57</v>
       </c>
       <c r="G758" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H758" t="s">
         <v>15</v>
@@ -23827,7 +23830,7 @@
     </row>
     <row r="759">
       <c r="A759" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B759" t="s">
         <v>9</v>
@@ -23853,7 +23856,7 @@
     </row>
     <row r="760">
       <c r="A760" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B760" t="s">
         <v>9</v>
@@ -23879,7 +23882,7 @@
     </row>
     <row r="761">
       <c r="A761" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B761" t="s">
         <v>9</v>
@@ -23905,7 +23908,7 @@
     </row>
     <row r="762">
       <c r="A762" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B762" t="s">
         <v>9</v>
@@ -23931,7 +23934,7 @@
     </row>
     <row r="763">
       <c r="A763" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B763" t="s">
         <v>9</v>
@@ -23957,7 +23960,7 @@
     </row>
     <row r="764">
       <c r="A764" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B764" t="s">
         <v>9</v>
@@ -23983,7 +23986,7 @@
     </row>
     <row r="765">
       <c r="A765" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B765" t="s">
         <v>9</v>
@@ -24009,7 +24012,7 @@
     </row>
     <row r="766">
       <c r="A766" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B766" t="s">
         <v>9</v>
@@ -24035,7 +24038,7 @@
     </row>
     <row r="767">
       <c r="A767" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B767" t="s">
         <v>9</v>
@@ -24061,7 +24064,7 @@
     </row>
     <row r="768">
       <c r="A768" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B768" t="s">
         <v>9</v>
@@ -24087,7 +24090,7 @@
     </row>
     <row r="769">
       <c r="A769" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B769" t="s">
         <v>9</v>
@@ -24113,7 +24116,7 @@
     </row>
     <row r="770">
       <c r="A770" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B770" t="s">
         <v>9</v>
@@ -24139,7 +24142,7 @@
     </row>
     <row r="771">
       <c r="A771" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B771" t="s">
         <v>9</v>
@@ -24165,7 +24168,7 @@
     </row>
     <row r="772">
       <c r="A772" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B772" t="s">
         <v>9</v>
@@ -24191,7 +24194,7 @@
     </row>
     <row r="773">
       <c r="A773" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B773" t="s">
         <v>9</v>
@@ -24217,7 +24220,7 @@
     </row>
     <row r="774">
       <c r="A774" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B774" t="s">
         <v>9</v>
@@ -24243,7 +24246,7 @@
     </row>
     <row r="775">
       <c r="A775" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B775" t="s">
         <v>9</v>
@@ -24269,7 +24272,7 @@
     </row>
     <row r="776">
       <c r="A776" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B776" t="s">
         <v>9</v>
@@ -24295,7 +24298,7 @@
     </row>
     <row r="777">
       <c r="A777" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B777" t="s">
         <v>9</v>
@@ -24321,7 +24324,7 @@
     </row>
     <row r="778">
       <c r="A778" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B778" t="s">
         <v>9</v>
@@ -24333,13 +24336,13 @@
         <v>66</v>
       </c>
       <c r="E778" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F778" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="G778" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H778" t="s">
         <v>15</v>
@@ -24347,7 +24350,7 @@
     </row>
     <row r="779">
       <c r="A779" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B779" t="s">
         <v>9</v>
@@ -24373,7 +24376,7 @@
     </row>
     <row r="780">
       <c r="A780" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B780" t="s">
         <v>9</v>
@@ -24394,12 +24397,12 @@
         <v>15</v>
       </c>
       <c r="H780" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B781" t="s">
         <v>9</v>
@@ -24425,7 +24428,7 @@
     </row>
     <row r="782">
       <c r="A782" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B782" t="s">
         <v>9</v>
@@ -24443,7 +24446,7 @@
         <v>371</v>
       </c>
       <c r="G782" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H782" t="s">
         <v>15</v>
@@ -24451,7 +24454,7 @@
     </row>
     <row r="783">
       <c r="A783" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B783" t="s">
         <v>9</v>
@@ -24477,25 +24480,25 @@
     </row>
     <row r="784">
       <c r="A784" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B784" t="s">
         <v>9</v>
       </c>
       <c r="C784" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="D784" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="E784" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="F784" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="G784" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H784" t="s">
         <v>15</v>
@@ -24503,7 +24506,7 @@
     </row>
     <row r="785">
       <c r="A785" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B785" t="s">
         <v>9</v>
@@ -24529,7 +24532,7 @@
     </row>
     <row r="786">
       <c r="A786" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B786" t="s">
         <v>9</v>
@@ -24555,7 +24558,7 @@
     </row>
     <row r="787">
       <c r="A787" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B787" t="s">
         <v>9</v>
@@ -24581,7 +24584,7 @@
     </row>
     <row r="788">
       <c r="A788" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B788" t="s">
         <v>9</v>
@@ -24607,7 +24610,7 @@
     </row>
     <row r="789">
       <c r="A789" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B789" t="s">
         <v>9</v>
@@ -24633,7 +24636,7 @@
     </row>
     <row r="790">
       <c r="A790" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B790" t="s">
         <v>9</v>
@@ -24659,7 +24662,7 @@
     </row>
     <row r="791">
       <c r="A791" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B791" t="s">
         <v>9</v>
@@ -24685,7 +24688,7 @@
     </row>
     <row r="792">
       <c r="A792" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B792" t="s">
         <v>9</v>
@@ -24711,7 +24714,7 @@
     </row>
     <row r="793">
       <c r="A793" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B793" t="s">
         <v>9</v>
@@ -24737,7 +24740,7 @@
     </row>
     <row r="794">
       <c r="A794" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B794" t="s">
         <v>9</v>
@@ -24763,7 +24766,7 @@
     </row>
     <row r="795">
       <c r="A795" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B795" t="s">
         <v>9</v>
@@ -24789,7 +24792,7 @@
     </row>
     <row r="796">
       <c r="A796" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B796" t="s">
         <v>9</v>
@@ -24815,7 +24818,7 @@
     </row>
     <row r="797">
       <c r="A797" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B797" t="s">
         <v>9</v>
@@ -24841,7 +24844,7 @@
     </row>
     <row r="798">
       <c r="A798" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B798" t="s">
         <v>9</v>
@@ -24867,7 +24870,7 @@
     </row>
     <row r="799">
       <c r="A799" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B799" t="s">
         <v>9</v>
@@ -24893,7 +24896,7 @@
     </row>
     <row r="800">
       <c r="A800" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B800" t="s">
         <v>9</v>
@@ -24919,7 +24922,7 @@
     </row>
     <row r="801">
       <c r="A801" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B801" t="s">
         <v>9</v>
@@ -24945,7 +24948,7 @@
     </row>
     <row r="802">
       <c r="A802" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B802" t="s">
         <v>9</v>
@@ -24963,7 +24966,7 @@
         <v>45</v>
       </c>
       <c r="G802" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H802" t="s">
         <v>15</v>
@@ -24971,7 +24974,7 @@
     </row>
     <row r="803">
       <c r="A803" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B803" t="s">
         <v>9</v>
@@ -24997,7 +25000,7 @@
     </row>
     <row r="804">
       <c r="A804" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B804" t="s">
         <v>9</v>
@@ -25023,7 +25026,7 @@
     </row>
     <row r="805">
       <c r="A805" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B805" t="s">
         <v>9</v>
@@ -25044,12 +25047,12 @@
         <v>331</v>
       </c>
       <c r="H805" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B806" t="s">
         <v>9</v>
@@ -25075,7 +25078,7 @@
     </row>
     <row r="807">
       <c r="A807" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B807" t="s">
         <v>9</v>
@@ -25101,7 +25104,7 @@
     </row>
     <row r="808">
       <c r="A808" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B808" t="s">
         <v>9</v>
@@ -25127,7 +25130,7 @@
     </row>
     <row r="809">
       <c r="A809" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B809" t="s">
         <v>9</v>
@@ -25153,7 +25156,7 @@
     </row>
     <row r="810">
       <c r="A810" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B810" t="s">
         <v>9</v>
@@ -25179,7 +25182,7 @@
     </row>
     <row r="811">
       <c r="A811" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B811" t="s">
         <v>9</v>
@@ -25205,7 +25208,7 @@
     </row>
     <row r="812">
       <c r="A812" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B812" t="s">
         <v>9</v>
@@ -25231,7 +25234,7 @@
     </row>
     <row r="813">
       <c r="A813" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B813" t="s">
         <v>9</v>
@@ -25257,7 +25260,7 @@
     </row>
     <row r="814">
       <c r="A814" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B814" t="s">
         <v>9</v>
@@ -25283,7 +25286,7 @@
     </row>
     <row r="815">
       <c r="A815" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B815" t="s">
         <v>9</v>
@@ -25309,7 +25312,7 @@
     </row>
     <row r="816">
       <c r="A816" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B816" t="s">
         <v>9</v>
@@ -25335,7 +25338,7 @@
     </row>
     <row r="817">
       <c r="A817" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B817" t="s">
         <v>9</v>
@@ -25361,7 +25364,7 @@
     </row>
     <row r="818">
       <c r="A818" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B818" t="s">
         <v>9</v>
@@ -25387,25 +25390,25 @@
     </row>
     <row r="819">
       <c r="A819" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B819" t="s">
         <v>9</v>
       </c>
       <c r="C819" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D819" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="E819" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="F819" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="G819" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H819" t="s">
         <v>15</v>
@@ -25413,7 +25416,7 @@
     </row>
     <row r="820">
       <c r="A820" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B820" t="s">
         <v>9</v>
@@ -25439,7 +25442,7 @@
     </row>
     <row r="821">
       <c r="A821" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B821" t="s">
         <v>9</v>
@@ -25465,7 +25468,7 @@
     </row>
     <row r="822">
       <c r="A822" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B822" t="s">
         <v>9</v>
@@ -25491,7 +25494,7 @@
     </row>
     <row r="823">
       <c r="A823" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B823" t="s">
         <v>9</v>
@@ -25517,7 +25520,7 @@
     </row>
     <row r="824">
       <c r="A824" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B824" t="s">
         <v>9</v>
@@ -25543,7 +25546,7 @@
     </row>
     <row r="825">
       <c r="A825" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B825" t="s">
         <v>9</v>
@@ -25569,7 +25572,7 @@
     </row>
     <row r="826">
       <c r="A826" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B826" t="s">
         <v>9</v>
@@ -25587,7 +25590,7 @@
         <v>68</v>
       </c>
       <c r="G826" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H826" t="s">
         <v>15</v>
@@ -25595,7 +25598,7 @@
     </row>
     <row r="827">
       <c r="A827" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B827" t="s">
         <v>9</v>
@@ -25621,7 +25624,7 @@
     </row>
     <row r="828">
       <c r="A828" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B828" t="s">
         <v>9</v>
@@ -25647,7 +25650,7 @@
     </row>
     <row r="829">
       <c r="A829" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B829" t="s">
         <v>9</v>
@@ -25673,7 +25676,7 @@
     </row>
     <row r="830">
       <c r="A830" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B830" t="s">
         <v>9</v>
@@ -25685,10 +25688,10 @@
         <v>29</v>
       </c>
       <c r="E830" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="F830" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="G830" t="s">
         <v>15</v>
@@ -25699,7 +25702,7 @@
     </row>
     <row r="831">
       <c r="A831" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B831" t="s">
         <v>9</v>
@@ -25725,7 +25728,7 @@
     </row>
     <row r="832">
       <c r="A832" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B832" t="s">
         <v>9</v>
@@ -25751,7 +25754,7 @@
     </row>
     <row r="833">
       <c r="A833" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B833" t="s">
         <v>9</v>
@@ -25777,7 +25780,7 @@
     </row>
     <row r="834">
       <c r="A834" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B834" t="s">
         <v>9</v>
@@ -25803,7 +25806,7 @@
     </row>
     <row r="835">
       <c r="A835" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B835" t="s">
         <v>9</v>
@@ -25829,7 +25832,7 @@
     </row>
     <row r="836">
       <c r="A836" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B836" t="s">
         <v>9</v>
@@ -25855,7 +25858,7 @@
     </row>
     <row r="837">
       <c r="A837" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B837" t="s">
         <v>9</v>
@@ -25881,7 +25884,7 @@
     </row>
     <row r="838">
       <c r="A838" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B838" t="s">
         <v>9</v>
@@ -25907,7 +25910,7 @@
     </row>
     <row r="839">
       <c r="A839" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B839" t="s">
         <v>9</v>
@@ -25933,7 +25936,7 @@
     </row>
     <row r="840">
       <c r="A840" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B840" t="s">
         <v>9</v>
@@ -25959,7 +25962,7 @@
     </row>
     <row r="841">
       <c r="A841" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B841" t="s">
         <v>9</v>
@@ -25985,7 +25988,7 @@
     </row>
     <row r="842">
       <c r="A842" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B842" t="s">
         <v>9</v>
@@ -26011,7 +26014,7 @@
     </row>
     <row r="843">
       <c r="A843" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B843" t="s">
         <v>9</v>
@@ -26023,10 +26026,10 @@
         <v>29</v>
       </c>
       <c r="E843" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="F843" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="G843" t="s">
         <v>15</v>
@@ -26037,7 +26040,7 @@
     </row>
     <row r="844">
       <c r="A844" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B844" t="s">
         <v>9</v>
@@ -26063,7 +26066,7 @@
     </row>
     <row r="845">
       <c r="A845" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B845" t="s">
         <v>9</v>
@@ -26089,7 +26092,7 @@
     </row>
     <row r="846">
       <c r="A846" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B846" t="s">
         <v>9</v>
@@ -26115,7 +26118,7 @@
     </row>
     <row r="847">
       <c r="A847" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B847" t="s">
         <v>9</v>
@@ -26141,7 +26144,7 @@
     </row>
     <row r="848">
       <c r="A848" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B848" t="s">
         <v>9</v>
@@ -26167,7 +26170,7 @@
     </row>
     <row r="849">
       <c r="A849" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B849" t="s">
         <v>9</v>
@@ -26182,10 +26185,10 @@
         <v>12</v>
       </c>
       <c r="F849" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G849" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H849" t="s">
         <v>15</v>
@@ -26193,7 +26196,7 @@
     </row>
     <row r="850">
       <c r="A850" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B850" t="s">
         <v>9</v>
@@ -26219,7 +26222,7 @@
     </row>
     <row r="851">
       <c r="A851" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B851" t="s">
         <v>9</v>
@@ -26245,7 +26248,7 @@
     </row>
     <row r="852">
       <c r="A852" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B852" t="s">
         <v>9</v>
@@ -26271,7 +26274,7 @@
     </row>
     <row r="853">
       <c r="A853" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B853" t="s">
         <v>9</v>
@@ -26297,7 +26300,7 @@
     </row>
     <row r="854">
       <c r="A854" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B854" t="s">
         <v>9</v>
@@ -26323,7 +26326,7 @@
     </row>
     <row r="855">
       <c r="A855" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B855" t="s">
         <v>9</v>
@@ -26349,7 +26352,7 @@
     </row>
     <row r="856">
       <c r="A856" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B856" t="s">
         <v>9</v>
@@ -26375,7 +26378,7 @@
     </row>
     <row r="857">
       <c r="A857" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B857" t="s">
         <v>9</v>
@@ -26401,7 +26404,7 @@
     </row>
     <row r="858">
       <c r="A858" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B858" t="s">
         <v>9</v>
@@ -26427,7 +26430,7 @@
     </row>
     <row r="859">
       <c r="A859" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B859" t="s">
         <v>9</v>
@@ -26445,7 +26448,7 @@
         <v>68</v>
       </c>
       <c r="G859" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H859" t="s">
         <v>15</v>
@@ -26453,7 +26456,7 @@
     </row>
     <row r="860">
       <c r="A860" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B860" t="s">
         <v>9</v>
@@ -26479,7 +26482,7 @@
     </row>
     <row r="861">
       <c r="A861" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B861" t="s">
         <v>9</v>
@@ -26505,7 +26508,7 @@
     </row>
     <row r="862">
       <c r="A862" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B862" t="s">
         <v>9</v>
@@ -26531,7 +26534,7 @@
     </row>
     <row r="863">
       <c r="A863" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B863" t="s">
         <v>9</v>
@@ -26557,7 +26560,7 @@
     </row>
     <row r="864">
       <c r="A864" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B864" t="s">
         <v>9</v>
@@ -26583,7 +26586,7 @@
     </row>
     <row r="865">
       <c r="A865" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B865" t="s">
         <v>9</v>
@@ -26609,7 +26612,7 @@
     </row>
     <row r="866">
       <c r="A866" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B866" t="s">
         <v>9</v>
@@ -26635,7 +26638,7 @@
     </row>
     <row r="867">
       <c r="A867" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B867" t="s">
         <v>9</v>
@@ -26661,7 +26664,7 @@
     </row>
     <row r="868">
       <c r="A868" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B868" t="s">
         <v>9</v>
@@ -26687,7 +26690,7 @@
     </row>
     <row r="869">
       <c r="A869" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B869" t="s">
         <v>9</v>
@@ -26713,7 +26716,7 @@
     </row>
     <row r="870">
       <c r="A870" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B870" t="s">
         <v>9</v>
@@ -26739,7 +26742,7 @@
     </row>
     <row r="871">
       <c r="A871" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B871" t="s">
         <v>9</v>
@@ -26765,7 +26768,7 @@
     </row>
     <row r="872">
       <c r="A872" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B872" t="s">
         <v>9</v>
@@ -26791,7 +26794,7 @@
     </row>
     <row r="873">
       <c r="A873" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B873" t="s">
         <v>9</v>
@@ -26817,7 +26820,7 @@
     </row>
     <row r="874">
       <c r="A874" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B874" t="s">
         <v>9</v>
@@ -26843,7 +26846,7 @@
     </row>
     <row r="875">
       <c r="A875" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B875" t="s">
         <v>9</v>
@@ -26869,7 +26872,7 @@
     </row>
     <row r="876">
       <c r="A876" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B876" t="s">
         <v>9</v>
@@ -26895,7 +26898,7 @@
     </row>
     <row r="877">
       <c r="A877" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B877" t="s">
         <v>9</v>
@@ -26921,7 +26924,7 @@
     </row>
     <row r="878">
       <c r="A878" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B878" t="s">
         <v>9</v>
@@ -26947,7 +26950,7 @@
     </row>
     <row r="879">
       <c r="A879" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B879" t="s">
         <v>9</v>
@@ -26965,7 +26968,7 @@
         <v>57</v>
       </c>
       <c r="G879" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H879" t="s">
         <v>15</v>
@@ -26973,7 +26976,7 @@
     </row>
     <row r="880">
       <c r="A880" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B880" t="s">
         <v>9</v>
@@ -26991,7 +26994,7 @@
         <v>45</v>
       </c>
       <c r="G880" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H880" t="s">
         <v>212</v>
@@ -26999,7 +27002,7 @@
     </row>
     <row r="881">
       <c r="A881" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B881" t="s">
         <v>9</v>
@@ -27025,7 +27028,7 @@
     </row>
     <row r="882">
       <c r="A882" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B882" t="s">
         <v>9</v>
@@ -27051,7 +27054,7 @@
     </row>
     <row r="883">
       <c r="A883" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B883" t="s">
         <v>9</v>
@@ -27069,7 +27072,7 @@
         <v>76</v>
       </c>
       <c r="G883" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H883" t="s">
         <v>15</v>
@@ -27077,7 +27080,7 @@
     </row>
     <row r="884">
       <c r="A884" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B884" t="s">
         <v>9</v>
@@ -27103,7 +27106,7 @@
     </row>
     <row r="885">
       <c r="A885" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B885" t="s">
         <v>9</v>
@@ -27121,7 +27124,7 @@
         <v>277</v>
       </c>
       <c r="G885" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H885" t="s">
         <v>15</v>
@@ -27129,7 +27132,7 @@
     </row>
     <row r="886">
       <c r="A886" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B886" t="s">
         <v>9</v>
@@ -27155,7 +27158,7 @@
     </row>
     <row r="887">
       <c r="A887" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B887" t="s">
         <v>9</v>
@@ -27181,7 +27184,7 @@
     </row>
     <row r="888">
       <c r="A888" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B888" t="s">
         <v>9</v>
@@ -27207,7 +27210,7 @@
     </row>
     <row r="889">
       <c r="A889" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B889" t="s">
         <v>9</v>
@@ -27233,7 +27236,7 @@
     </row>
     <row r="890">
       <c r="A890" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B890" t="s">
         <v>9</v>
@@ -27259,7 +27262,7 @@
     </row>
     <row r="891">
       <c r="A891" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B891" t="s">
         <v>9</v>
@@ -27285,7 +27288,7 @@
     </row>
     <row r="892">
       <c r="A892" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B892" t="s">
         <v>9</v>
@@ -27311,7 +27314,7 @@
     </row>
     <row r="893">
       <c r="A893" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B893" t="s">
         <v>9</v>
@@ -27337,7 +27340,7 @@
     </row>
     <row r="894">
       <c r="A894" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B894" t="s">
         <v>9</v>
@@ -27363,7 +27366,7 @@
     </row>
     <row r="895">
       <c r="A895" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B895" t="s">
         <v>9</v>
@@ -27389,7 +27392,7 @@
     </row>
     <row r="896">
       <c r="A896" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B896" t="s">
         <v>9</v>
@@ -27415,7 +27418,7 @@
     </row>
     <row r="897">
       <c r="A897" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B897" t="s">
         <v>9</v>
@@ -27441,7 +27444,7 @@
     </row>
     <row r="898">
       <c r="A898" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B898" t="s">
         <v>9</v>
@@ -27467,7 +27470,7 @@
     </row>
     <row r="899">
       <c r="A899" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B899" t="s">
         <v>15</v>
@@ -27493,7 +27496,7 @@
     </row>
     <row r="900">
       <c r="A900" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B900" t="s">
         <v>9</v>
@@ -27519,7 +27522,7 @@
     </row>
     <row r="901">
       <c r="A901" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B901" t="s">
         <v>9</v>
@@ -27545,7 +27548,7 @@
     </row>
     <row r="902">
       <c r="A902" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B902" t="s">
         <v>9</v>
@@ -27571,7 +27574,7 @@
     </row>
     <row r="903">
       <c r="A903" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B903" t="s">
         <v>9</v>

--- a/data/derived_data/2_RarefyData/Dataset_2/ps_16S_cl_Dataset_2_tax_table.xlsx
+++ b/data/derived_data/2_RarefyData/Dataset_2/ps_16S_cl_Dataset_2_tax_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="1260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="1261">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -3216,6 +3216,9 @@
   </si>
   <si>
     <t xml:space="preserve">Cluster_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gluconobacter cerinus</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_600</t>
@@ -8661,7 +8664,7 @@
         <v>48</v>
       </c>
       <c r="F175" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="G175" t="s">
         <v>15</v>
@@ -23305,12 +23308,12 @@
         <v>60</v>
       </c>
       <c r="H738" t="s">
-        <v>15</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B739" t="s">
         <v>9</v>
@@ -23319,16 +23322,16 @@
         <v>65</v>
       </c>
       <c r="D739" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="E739" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F739" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="G739" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H739" t="s">
         <v>15</v>
@@ -23336,7 +23339,7 @@
     </row>
     <row r="740">
       <c r="A740" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B740" t="s">
         <v>9</v>
@@ -23354,7 +23357,7 @@
         <v>231</v>
       </c>
       <c r="G740" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H740" t="s">
         <v>15</v>
@@ -23362,7 +23365,7 @@
     </row>
     <row r="741">
       <c r="A741" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B741" t="s">
         <v>9</v>
@@ -23388,7 +23391,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B742" t="s">
         <v>9</v>
@@ -23414,7 +23417,7 @@
     </row>
     <row r="743">
       <c r="A743" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B743" t="s">
         <v>9</v>
@@ -23440,7 +23443,7 @@
     </row>
     <row r="744">
       <c r="A744" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B744" t="s">
         <v>9</v>
@@ -23466,7 +23469,7 @@
     </row>
     <row r="745">
       <c r="A745" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B745" t="s">
         <v>9</v>
@@ -23492,7 +23495,7 @@
     </row>
     <row r="746">
       <c r="A746" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B746" t="s">
         <v>9</v>
@@ -23510,7 +23513,7 @@
         <v>76</v>
       </c>
       <c r="G746" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H746" t="s">
         <v>15</v>
@@ -23518,7 +23521,7 @@
     </row>
     <row r="747">
       <c r="A747" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B747" t="s">
         <v>9</v>
@@ -23544,7 +23547,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B748" t="s">
         <v>9</v>
@@ -23562,7 +23565,7 @@
         <v>68</v>
       </c>
       <c r="G748" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H748" t="s">
         <v>15</v>
@@ -23570,7 +23573,7 @@
     </row>
     <row r="749">
       <c r="A749" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B749" t="s">
         <v>9</v>
@@ -23596,7 +23599,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B750" t="s">
         <v>9</v>
@@ -23622,7 +23625,7 @@
     </row>
     <row r="751">
       <c r="A751" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B751" t="s">
         <v>9</v>
@@ -23648,7 +23651,7 @@
     </row>
     <row r="752">
       <c r="A752" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B752" t="s">
         <v>9</v>
@@ -23674,7 +23677,7 @@
     </row>
     <row r="753">
       <c r="A753" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B753" t="s">
         <v>9</v>
@@ -23700,7 +23703,7 @@
     </row>
     <row r="754">
       <c r="A754" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B754" t="s">
         <v>9</v>
@@ -23726,7 +23729,7 @@
     </row>
     <row r="755">
       <c r="A755" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B755" t="s">
         <v>9</v>
@@ -23752,7 +23755,7 @@
     </row>
     <row r="756">
       <c r="A756" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B756" t="s">
         <v>9</v>
@@ -23778,7 +23781,7 @@
     </row>
     <row r="757">
       <c r="A757" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B757" t="s">
         <v>9</v>
@@ -23804,7 +23807,7 @@
     </row>
     <row r="758">
       <c r="A758" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B758" t="s">
         <v>9</v>
@@ -23830,7 +23833,7 @@
     </row>
     <row r="759">
       <c r="A759" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B759" t="s">
         <v>9</v>
@@ -23856,7 +23859,7 @@
     </row>
     <row r="760">
       <c r="A760" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B760" t="s">
         <v>9</v>
@@ -23882,7 +23885,7 @@
     </row>
     <row r="761">
       <c r="A761" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B761" t="s">
         <v>9</v>
@@ -23908,7 +23911,7 @@
     </row>
     <row r="762">
       <c r="A762" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B762" t="s">
         <v>9</v>
@@ -23934,7 +23937,7 @@
     </row>
     <row r="763">
       <c r="A763" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B763" t="s">
         <v>9</v>
@@ -23960,7 +23963,7 @@
     </row>
     <row r="764">
       <c r="A764" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B764" t="s">
         <v>9</v>
@@ -23986,7 +23989,7 @@
     </row>
     <row r="765">
       <c r="A765" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B765" t="s">
         <v>9</v>
@@ -24012,7 +24015,7 @@
     </row>
     <row r="766">
       <c r="A766" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B766" t="s">
         <v>9</v>
@@ -24038,7 +24041,7 @@
     </row>
     <row r="767">
       <c r="A767" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B767" t="s">
         <v>9</v>
@@ -24064,7 +24067,7 @@
     </row>
     <row r="768">
       <c r="A768" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B768" t="s">
         <v>9</v>
@@ -24090,7 +24093,7 @@
     </row>
     <row r="769">
       <c r="A769" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B769" t="s">
         <v>9</v>
@@ -24116,7 +24119,7 @@
     </row>
     <row r="770">
       <c r="A770" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B770" t="s">
         <v>9</v>
@@ -24142,7 +24145,7 @@
     </row>
     <row r="771">
       <c r="A771" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B771" t="s">
         <v>9</v>
@@ -24168,7 +24171,7 @@
     </row>
     <row r="772">
       <c r="A772" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B772" t="s">
         <v>9</v>
@@ -24194,7 +24197,7 @@
     </row>
     <row r="773">
       <c r="A773" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B773" t="s">
         <v>9</v>
@@ -24220,7 +24223,7 @@
     </row>
     <row r="774">
       <c r="A774" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B774" t="s">
         <v>9</v>
@@ -24246,7 +24249,7 @@
     </row>
     <row r="775">
       <c r="A775" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B775" t="s">
         <v>9</v>
@@ -24272,7 +24275,7 @@
     </row>
     <row r="776">
       <c r="A776" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B776" t="s">
         <v>9</v>
@@ -24298,7 +24301,7 @@
     </row>
     <row r="777">
       <c r="A777" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B777" t="s">
         <v>9</v>
@@ -24324,7 +24327,7 @@
     </row>
     <row r="778">
       <c r="A778" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B778" t="s">
         <v>9</v>
@@ -24336,13 +24339,13 @@
         <v>66</v>
       </c>
       <c r="E778" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="F778" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="G778" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H778" t="s">
         <v>15</v>
@@ -24350,7 +24353,7 @@
     </row>
     <row r="779">
       <c r="A779" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B779" t="s">
         <v>9</v>
@@ -24376,7 +24379,7 @@
     </row>
     <row r="780">
       <c r="A780" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B780" t="s">
         <v>9</v>
@@ -24397,12 +24400,12 @@
         <v>15</v>
       </c>
       <c r="H780" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B781" t="s">
         <v>9</v>
@@ -24428,7 +24431,7 @@
     </row>
     <row r="782">
       <c r="A782" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B782" t="s">
         <v>9</v>
@@ -24446,7 +24449,7 @@
         <v>371</v>
       </c>
       <c r="G782" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H782" t="s">
         <v>15</v>
@@ -24454,7 +24457,7 @@
     </row>
     <row r="783">
       <c r="A783" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B783" t="s">
         <v>9</v>
@@ -24480,25 +24483,25 @@
     </row>
     <row r="784">
       <c r="A784" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B784" t="s">
         <v>9</v>
       </c>
       <c r="C784" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D784" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E784" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="F784" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G784" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H784" t="s">
         <v>15</v>
@@ -24506,7 +24509,7 @@
     </row>
     <row r="785">
       <c r="A785" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B785" t="s">
         <v>9</v>
@@ -24532,7 +24535,7 @@
     </row>
     <row r="786">
       <c r="A786" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B786" t="s">
         <v>9</v>
@@ -24558,7 +24561,7 @@
     </row>
     <row r="787">
       <c r="A787" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B787" t="s">
         <v>9</v>
@@ -24584,7 +24587,7 @@
     </row>
     <row r="788">
       <c r="A788" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B788" t="s">
         <v>9</v>
@@ -24610,7 +24613,7 @@
     </row>
     <row r="789">
       <c r="A789" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B789" t="s">
         <v>9</v>
@@ -24636,7 +24639,7 @@
     </row>
     <row r="790">
       <c r="A790" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B790" t="s">
         <v>9</v>
@@ -24662,7 +24665,7 @@
     </row>
     <row r="791">
       <c r="A791" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B791" t="s">
         <v>9</v>
@@ -24688,7 +24691,7 @@
     </row>
     <row r="792">
       <c r="A792" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B792" t="s">
         <v>9</v>
@@ -24714,7 +24717,7 @@
     </row>
     <row r="793">
       <c r="A793" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B793" t="s">
         <v>9</v>
@@ -24740,7 +24743,7 @@
     </row>
     <row r="794">
       <c r="A794" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B794" t="s">
         <v>9</v>
@@ -24766,7 +24769,7 @@
     </row>
     <row r="795">
       <c r="A795" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B795" t="s">
         <v>9</v>
@@ -24792,7 +24795,7 @@
     </row>
     <row r="796">
       <c r="A796" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B796" t="s">
         <v>9</v>
@@ -24818,7 +24821,7 @@
     </row>
     <row r="797">
       <c r="A797" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B797" t="s">
         <v>9</v>
@@ -24844,7 +24847,7 @@
     </row>
     <row r="798">
       <c r="A798" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B798" t="s">
         <v>9</v>
@@ -24870,7 +24873,7 @@
     </row>
     <row r="799">
       <c r="A799" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B799" t="s">
         <v>9</v>
@@ -24896,7 +24899,7 @@
     </row>
     <row r="800">
       <c r="A800" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B800" t="s">
         <v>9</v>
@@ -24922,7 +24925,7 @@
     </row>
     <row r="801">
       <c r="A801" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B801" t="s">
         <v>9</v>
@@ -24948,7 +24951,7 @@
     </row>
     <row r="802">
       <c r="A802" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B802" t="s">
         <v>9</v>
@@ -24966,7 +24969,7 @@
         <v>45</v>
       </c>
       <c r="G802" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H802" t="s">
         <v>15</v>
@@ -24974,7 +24977,7 @@
     </row>
     <row r="803">
       <c r="A803" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B803" t="s">
         <v>9</v>
@@ -25000,7 +25003,7 @@
     </row>
     <row r="804">
       <c r="A804" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B804" t="s">
         <v>9</v>
@@ -25026,7 +25029,7 @@
     </row>
     <row r="805">
       <c r="A805" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B805" t="s">
         <v>9</v>
@@ -25047,12 +25050,12 @@
         <v>331</v>
       </c>
       <c r="H805" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B806" t="s">
         <v>9</v>
@@ -25078,7 +25081,7 @@
     </row>
     <row r="807">
       <c r="A807" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B807" t="s">
         <v>9</v>
@@ -25104,7 +25107,7 @@
     </row>
     <row r="808">
       <c r="A808" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B808" t="s">
         <v>9</v>
@@ -25130,7 +25133,7 @@
     </row>
     <row r="809">
       <c r="A809" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B809" t="s">
         <v>9</v>
@@ -25156,7 +25159,7 @@
     </row>
     <row r="810">
       <c r="A810" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B810" t="s">
         <v>9</v>
@@ -25182,7 +25185,7 @@
     </row>
     <row r="811">
       <c r="A811" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B811" t="s">
         <v>9</v>
@@ -25208,7 +25211,7 @@
     </row>
     <row r="812">
       <c r="A812" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B812" t="s">
         <v>9</v>
@@ -25234,7 +25237,7 @@
     </row>
     <row r="813">
       <c r="A813" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B813" t="s">
         <v>9</v>
@@ -25260,7 +25263,7 @@
     </row>
     <row r="814">
       <c r="A814" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B814" t="s">
         <v>9</v>
@@ -25286,7 +25289,7 @@
     </row>
     <row r="815">
       <c r="A815" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B815" t="s">
         <v>9</v>
@@ -25312,7 +25315,7 @@
     </row>
     <row r="816">
       <c r="A816" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B816" t="s">
         <v>9</v>
@@ -25338,7 +25341,7 @@
     </row>
     <row r="817">
       <c r="A817" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B817" t="s">
         <v>9</v>
@@ -25364,7 +25367,7 @@
     </row>
     <row r="818">
       <c r="A818" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B818" t="s">
         <v>9</v>
@@ -25390,7 +25393,7 @@
     </row>
     <row r="819">
       <c r="A819" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B819" t="s">
         <v>9</v>
@@ -25399,16 +25402,16 @@
         <v>1035</v>
       </c>
       <c r="D819" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="E819" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="F819" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="G819" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H819" t="s">
         <v>15</v>
@@ -25416,7 +25419,7 @@
     </row>
     <row r="820">
       <c r="A820" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B820" t="s">
         <v>9</v>
@@ -25442,7 +25445,7 @@
     </row>
     <row r="821">
       <c r="A821" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B821" t="s">
         <v>9</v>
@@ -25468,7 +25471,7 @@
     </row>
     <row r="822">
       <c r="A822" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B822" t="s">
         <v>9</v>
@@ -25494,7 +25497,7 @@
     </row>
     <row r="823">
       <c r="A823" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B823" t="s">
         <v>9</v>
@@ -25520,7 +25523,7 @@
     </row>
     <row r="824">
       <c r="A824" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B824" t="s">
         <v>9</v>
@@ -25546,7 +25549,7 @@
     </row>
     <row r="825">
       <c r="A825" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B825" t="s">
         <v>9</v>
@@ -25572,7 +25575,7 @@
     </row>
     <row r="826">
       <c r="A826" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B826" t="s">
         <v>9</v>
@@ -25590,7 +25593,7 @@
         <v>68</v>
       </c>
       <c r="G826" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H826" t="s">
         <v>15</v>
@@ -25598,7 +25601,7 @@
     </row>
     <row r="827">
       <c r="A827" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B827" t="s">
         <v>9</v>
@@ -25624,7 +25627,7 @@
     </row>
     <row r="828">
       <c r="A828" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B828" t="s">
         <v>9</v>
@@ -25650,7 +25653,7 @@
     </row>
     <row r="829">
       <c r="A829" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B829" t="s">
         <v>9</v>
@@ -25676,7 +25679,7 @@
     </row>
     <row r="830">
       <c r="A830" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B830" t="s">
         <v>9</v>
@@ -25688,10 +25691,10 @@
         <v>29</v>
       </c>
       <c r="E830" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="F830" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="G830" t="s">
         <v>15</v>
@@ -25702,7 +25705,7 @@
     </row>
     <row r="831">
       <c r="A831" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B831" t="s">
         <v>9</v>
@@ -25728,7 +25731,7 @@
     </row>
     <row r="832">
       <c r="A832" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B832" t="s">
         <v>9</v>
@@ -25754,7 +25757,7 @@
     </row>
     <row r="833">
       <c r="A833" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B833" t="s">
         <v>9</v>
@@ -25780,7 +25783,7 @@
     </row>
     <row r="834">
       <c r="A834" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B834" t="s">
         <v>9</v>
@@ -25806,7 +25809,7 @@
     </row>
     <row r="835">
       <c r="A835" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B835" t="s">
         <v>9</v>
@@ -25832,7 +25835,7 @@
     </row>
     <row r="836">
       <c r="A836" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B836" t="s">
         <v>9</v>
@@ -25858,7 +25861,7 @@
     </row>
     <row r="837">
       <c r="A837" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B837" t="s">
         <v>9</v>
@@ -25884,7 +25887,7 @@
     </row>
     <row r="838">
       <c r="A838" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B838" t="s">
         <v>9</v>
@@ -25910,7 +25913,7 @@
     </row>
     <row r="839">
       <c r="A839" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B839" t="s">
         <v>9</v>
@@ -25936,7 +25939,7 @@
     </row>
     <row r="840">
       <c r="A840" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B840" t="s">
         <v>9</v>
@@ -25962,7 +25965,7 @@
     </row>
     <row r="841">
       <c r="A841" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B841" t="s">
         <v>9</v>
@@ -25988,7 +25991,7 @@
     </row>
     <row r="842">
       <c r="A842" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B842" t="s">
         <v>9</v>
@@ -26014,7 +26017,7 @@
     </row>
     <row r="843">
       <c r="A843" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B843" t="s">
         <v>9</v>
@@ -26026,10 +26029,10 @@
         <v>29</v>
       </c>
       <c r="E843" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="F843" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="G843" t="s">
         <v>15</v>
@@ -26040,7 +26043,7 @@
     </row>
     <row r="844">
       <c r="A844" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B844" t="s">
         <v>9</v>
@@ -26066,7 +26069,7 @@
     </row>
     <row r="845">
       <c r="A845" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B845" t="s">
         <v>9</v>
@@ -26092,7 +26095,7 @@
     </row>
     <row r="846">
       <c r="A846" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B846" t="s">
         <v>9</v>
@@ -26118,7 +26121,7 @@
     </row>
     <row r="847">
       <c r="A847" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B847" t="s">
         <v>9</v>
@@ -26144,7 +26147,7 @@
     </row>
     <row r="848">
       <c r="A848" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B848" t="s">
         <v>9</v>
@@ -26170,7 +26173,7 @@
     </row>
     <row r="849">
       <c r="A849" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B849" t="s">
         <v>9</v>
@@ -26196,7 +26199,7 @@
     </row>
     <row r="850">
       <c r="A850" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B850" t="s">
         <v>9</v>
@@ -26222,7 +26225,7 @@
     </row>
     <row r="851">
       <c r="A851" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B851" t="s">
         <v>9</v>
@@ -26248,7 +26251,7 @@
     </row>
     <row r="852">
       <c r="A852" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B852" t="s">
         <v>9</v>
@@ -26274,7 +26277,7 @@
     </row>
     <row r="853">
       <c r="A853" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B853" t="s">
         <v>9</v>
@@ -26300,7 +26303,7 @@
     </row>
     <row r="854">
       <c r="A854" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B854" t="s">
         <v>9</v>
@@ -26326,7 +26329,7 @@
     </row>
     <row r="855">
       <c r="A855" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B855" t="s">
         <v>9</v>
@@ -26352,7 +26355,7 @@
     </row>
     <row r="856">
       <c r="A856" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B856" t="s">
         <v>9</v>
@@ -26378,7 +26381,7 @@
     </row>
     <row r="857">
       <c r="A857" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B857" t="s">
         <v>9</v>
@@ -26404,7 +26407,7 @@
     </row>
     <row r="858">
       <c r="A858" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B858" t="s">
         <v>9</v>
@@ -26430,7 +26433,7 @@
     </row>
     <row r="859">
       <c r="A859" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B859" t="s">
         <v>9</v>
@@ -26448,7 +26451,7 @@
         <v>68</v>
       </c>
       <c r="G859" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H859" t="s">
         <v>15</v>
@@ -26456,7 +26459,7 @@
     </row>
     <row r="860">
       <c r="A860" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B860" t="s">
         <v>9</v>
@@ -26482,7 +26485,7 @@
     </row>
     <row r="861">
       <c r="A861" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B861" t="s">
         <v>9</v>
@@ -26508,7 +26511,7 @@
     </row>
     <row r="862">
       <c r="A862" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B862" t="s">
         <v>9</v>
@@ -26534,7 +26537,7 @@
     </row>
     <row r="863">
       <c r="A863" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B863" t="s">
         <v>9</v>
@@ -26560,7 +26563,7 @@
     </row>
     <row r="864">
       <c r="A864" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B864" t="s">
         <v>9</v>
@@ -26586,7 +26589,7 @@
     </row>
     <row r="865">
       <c r="A865" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B865" t="s">
         <v>9</v>
@@ -26612,7 +26615,7 @@
     </row>
     <row r="866">
       <c r="A866" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B866" t="s">
         <v>9</v>
@@ -26638,7 +26641,7 @@
     </row>
     <row r="867">
       <c r="A867" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B867" t="s">
         <v>9</v>
@@ -26664,7 +26667,7 @@
     </row>
     <row r="868">
       <c r="A868" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B868" t="s">
         <v>9</v>
@@ -26690,7 +26693,7 @@
     </row>
     <row r="869">
       <c r="A869" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B869" t="s">
         <v>9</v>
@@ -26716,7 +26719,7 @@
     </row>
     <row r="870">
       <c r="A870" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B870" t="s">
         <v>9</v>
@@ -26742,7 +26745,7 @@
     </row>
     <row r="871">
       <c r="A871" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B871" t="s">
         <v>9</v>
@@ -26768,7 +26771,7 @@
     </row>
     <row r="872">
       <c r="A872" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B872" t="s">
         <v>9</v>
@@ -26794,7 +26797,7 @@
     </row>
     <row r="873">
       <c r="A873" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B873" t="s">
         <v>9</v>
@@ -26820,7 +26823,7 @@
     </row>
     <row r="874">
       <c r="A874" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B874" t="s">
         <v>9</v>
@@ -26846,7 +26849,7 @@
     </row>
     <row r="875">
       <c r="A875" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B875" t="s">
         <v>9</v>
@@ -26872,7 +26875,7 @@
     </row>
     <row r="876">
       <c r="A876" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B876" t="s">
         <v>9</v>
@@ -26898,7 +26901,7 @@
     </row>
     <row r="877">
       <c r="A877" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B877" t="s">
         <v>9</v>
@@ -26924,7 +26927,7 @@
     </row>
     <row r="878">
       <c r="A878" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B878" t="s">
         <v>9</v>
@@ -26950,7 +26953,7 @@
     </row>
     <row r="879">
       <c r="A879" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B879" t="s">
         <v>9</v>
@@ -26976,7 +26979,7 @@
     </row>
     <row r="880">
       <c r="A880" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B880" t="s">
         <v>9</v>
@@ -27002,7 +27005,7 @@
     </row>
     <row r="881">
       <c r="A881" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B881" t="s">
         <v>9</v>
@@ -27028,7 +27031,7 @@
     </row>
     <row r="882">
       <c r="A882" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B882" t="s">
         <v>9</v>
@@ -27054,7 +27057,7 @@
     </row>
     <row r="883">
       <c r="A883" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B883" t="s">
         <v>9</v>
@@ -27080,7 +27083,7 @@
     </row>
     <row r="884">
       <c r="A884" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B884" t="s">
         <v>9</v>
@@ -27106,7 +27109,7 @@
     </row>
     <row r="885">
       <c r="A885" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B885" t="s">
         <v>9</v>
@@ -27124,7 +27127,7 @@
         <v>277</v>
       </c>
       <c r="G885" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H885" t="s">
         <v>15</v>
@@ -27132,7 +27135,7 @@
     </row>
     <row r="886">
       <c r="A886" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B886" t="s">
         <v>9</v>
@@ -27158,7 +27161,7 @@
     </row>
     <row r="887">
       <c r="A887" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B887" t="s">
         <v>9</v>
@@ -27184,7 +27187,7 @@
     </row>
     <row r="888">
       <c r="A888" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B888" t="s">
         <v>9</v>
@@ -27210,7 +27213,7 @@
     </row>
     <row r="889">
       <c r="A889" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B889" t="s">
         <v>9</v>
@@ -27236,7 +27239,7 @@
     </row>
     <row r="890">
       <c r="A890" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B890" t="s">
         <v>9</v>
@@ -27262,7 +27265,7 @@
     </row>
     <row r="891">
       <c r="A891" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B891" t="s">
         <v>9</v>
@@ -27288,7 +27291,7 @@
     </row>
     <row r="892">
       <c r="A892" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B892" t="s">
         <v>9</v>
@@ -27314,7 +27317,7 @@
     </row>
     <row r="893">
       <c r="A893" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B893" t="s">
         <v>9</v>
@@ -27340,7 +27343,7 @@
     </row>
     <row r="894">
       <c r="A894" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B894" t="s">
         <v>9</v>
@@ -27366,7 +27369,7 @@
     </row>
     <row r="895">
       <c r="A895" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B895" t="s">
         <v>9</v>
@@ -27392,7 +27395,7 @@
     </row>
     <row r="896">
       <c r="A896" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B896" t="s">
         <v>9</v>
@@ -27418,7 +27421,7 @@
     </row>
     <row r="897">
       <c r="A897" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B897" t="s">
         <v>9</v>
@@ -27444,7 +27447,7 @@
     </row>
     <row r="898">
       <c r="A898" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B898" t="s">
         <v>9</v>
@@ -27470,7 +27473,7 @@
     </row>
     <row r="899">
       <c r="A899" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B899" t="s">
         <v>15</v>
@@ -27496,7 +27499,7 @@
     </row>
     <row r="900">
       <c r="A900" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B900" t="s">
         <v>9</v>
@@ -27522,7 +27525,7 @@
     </row>
     <row r="901">
       <c r="A901" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B901" t="s">
         <v>9</v>
@@ -27548,7 +27551,7 @@
     </row>
     <row r="902">
       <c r="A902" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B902" t="s">
         <v>9</v>
@@ -27574,7 +27577,7 @@
     </row>
     <row r="903">
       <c r="A903" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B903" t="s">
         <v>9</v>
